--- a/ZCloud-电力监管-001-20261020/powercor-2020-capex-reconciliation/validation/positive_cases/inside_tolerance.xlsx
+++ b/ZCloud-电力监管-001-20261020/powercor-2020-capex-reconciliation/validation/positive_cases/inside_tolerance.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>13.69059834417945</v>
+        <v>13.69159834417945</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
